--- a/artfynd/A 45088-2023 artfynd.xlsx
+++ b/artfynd/A 45088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121230186</v>
       </c>
       <c r="B2" t="n">
-        <v>109951</v>
+        <v>109961</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45088-2023 artfynd.xlsx
+++ b/artfynd/A 45088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121230186</v>
       </c>
       <c r="B2" t="n">
-        <v>109961</v>
+        <v>109974</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45088-2023 artfynd.xlsx
+++ b/artfynd/A 45088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121230186</v>
       </c>
       <c r="B2" t="n">
-        <v>109974</v>
+        <v>109975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45088-2023 artfynd.xlsx
+++ b/artfynd/A 45088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121230186</v>
       </c>
       <c r="B2" t="n">
-        <v>109975</v>
+        <v>109978</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45088-2023 artfynd.xlsx
+++ b/artfynd/A 45088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121230186</v>
       </c>
       <c r="B2" t="n">
-        <v>109978</v>
+        <v>109984</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45088-2023 artfynd.xlsx
+++ b/artfynd/A 45088-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121230186</v>
       </c>
       <c r="B2" t="n">
-        <v>109984</v>
+        <v>109985</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
